--- a/src/templates/template-importacao.xlsx
+++ b/src/templates/template-importacao.xlsx
@@ -21,168 +21,163 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
-  <si>
-    <t xml:space="preserve">📥 Template de Importação — Minhas Finanças</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preencha a partir da linha 5. Não altere as colunas. Salve como .xlsx antes de importar.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
+  <si>
+    <t xml:space="preserve">📥 Extrato Cartão de Crédito — Minhas Finanças</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesmo layout do extrato CSV exportado pelo banco — importe direto ou preencha manualmente.</t>
   </si>
   <si>
     <t xml:space="preserve">Data</t>
   </si>
   <si>
-    <t xml:space="preserve">Descrição</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor (R$)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Categoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observação (opcional)</t>
+    <t xml:space="preserve">Estabelecimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcela</t>
   </si>
   <si>
     <t xml:space="preserve">DD/MM/AAAA</t>
   </si>
   <si>
-    <t xml:space="preserve">Ex: Supermercado Pão de Açúcar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ex: 189,90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ex: Alimentação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Livre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supermercado Pão de Açúcar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alimentação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Posto Shell — Gasolina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transporte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netflix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lazer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assinatura mensal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Farmácia São Paulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saúde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restaurante Outback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jantar aniversário</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📋 INSTRUÇÕES DE PREENCHIMENTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. COLUNAS OBRIGATÓRIAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Data: use o formato DD/MM/AAAA (ex: 15/03/2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Descrição: nome da transação (ex: Supermercado Extra)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Valor (R$): use ponto ou vírgula como decimal (ex: 189.90 ou 189,90)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. COLUNA OPCIONAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Categoria: se preenchida, o sistema tentará mapear automaticamente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Você poderá ajustar na tela de preview antes de importar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Observação: campo livre, não é importado para o sistema.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. REMOVA AS LINHAS DE EXEMPLO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • As linhas 5 a 9 são exemplos. Apague-as antes de importar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Preencha a partir da linha 5 com suas transações reais.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. SALVE COMO .XLSX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Certifique-se de salvar o arquivo no formato Excel (.xlsx).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Arquivos .csv ou .xls não são suportados.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. IMPORT NO SISTEMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Acesse a tela Importar no menu de navegação.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Clique em 'Selecionar arquivo' ou arraste o .xlsx para a área indicada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Revise as transações na tabela de preview.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Ajuste as categorias se necessário.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  • Clique em 'Importar X despesas' para confirmar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠️  As despesas importadas aparecerão para TODOS os membros do grupo em tempo real.</t>
+    <t xml:space="preserve">Nome do estabelecimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome do portador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R$ 0,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ex: 1 de 3 ou -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEMON SUPERMERCADO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA CAROLINA BUENO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R$ 35,08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NETFLIX.COM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R$ 44,90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R$ 80,15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WN MEDICINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R$ 400,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 de 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COBASI-O SHOPPING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R$ 177,91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 de 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📋 INSTRUÇÕES — EXTRATO CARTÃO DE CRÉDITO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPÇÃO 1 — IMPORTAR CSV DIRETO DO BANCO (mais rápido)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1. No site/app do banco, exporte o extrato do período no formato CSV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2. Na tela de Importação do app, clique em 'Selecionar arquivo'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3. Selecione o arquivo .csv exportado pelo banco.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4. O sistema reconhecerá automaticamente o layout. Revise e importe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPÇÃO 2 — PREENCHER ESTE TEMPLATE (quando não há CSV disponível)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1. Remova as linhas de exemplo (5 a 9) e preencha a partir da linha 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2. Siga o formato de cada coluna conforme indicado na linha 4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3. Salve como .xlsx e importe na tela de Importação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLUNAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Data: DD/MM/AAAA — ex: 15/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Estabelecimento: nome do estabelecimento — ex: LEMON SUPERMERCADO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Portador: nome do titular — ex: ANA CAROLINA BUENO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Valor: formato R$ X,XX — ex: R$ 189,90 (negativos são ignorados automaticamente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  • Parcela: ex: 1 de 3, 2 de 10 ou - (traço para compra à vista)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️  Lançamentos negativos (pagamentos, estornos) são ignorados automaticamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️  Todas as despesas importadas aparecem para todos os membros do grupo em tempo real.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,21 +277,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF555555"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FFB71C1C"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF7B3F00"/>
@@ -305,7 +285,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,7 +301,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFFF0F0"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -345,12 +325,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFF0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF0F0"/>
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
@@ -410,7 +384,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -439,10 +413,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -451,11 +421,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -463,15 +429,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -479,14 +437,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -503,15 +453,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -543,7 +485,7 @@
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF777777"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FFB71C1C"/>
+      <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF3CD"/>
       <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FF660066"/>
@@ -559,7 +501,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFFFF0F0"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFD5E8D4"/>
       <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -771,10 +713,9 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -836,777 +777,783 @@
       <c r="B5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7" t="n">
-        <v>350.9</v>
+      <c r="C5" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="9" t="s">
+      <c r="D6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="10" t="n">
-        <v>180</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>55.9</v>
+        <v>21</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="9" t="s">
+      <c r="A8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="10" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="B8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="C8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>210</v>
+        <v>28</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
+      <c r="A36" s="9"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
     </row>
     <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="11"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
+      <c r="A38" s="9"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15"/>
-      <c r="B39" s="16"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
+      <c r="A39" s="11"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
     </row>
     <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
+      <c r="A40" s="9"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
+      <c r="A41" s="11"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
+      <c r="A42" s="9"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
     </row>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
+      <c r="A43" s="11"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
     </row>
     <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
+      <c r="A44" s="9"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
     </row>
     <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="15"/>
-      <c r="B45" s="16"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
+      <c r="A45" s="11"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
     </row>
     <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
+      <c r="A46" s="9"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
     </row>
     <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="15"/>
-      <c r="B47" s="16"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
+      <c r="A47" s="11"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
     </row>
     <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="11"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
     </row>
     <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="15"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
+      <c r="A49" s="11"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
     </row>
     <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="11"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
+      <c r="A50" s="9"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
     </row>
     <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="15"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
+      <c r="A51" s="11"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
     </row>
     <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="11"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
+      <c r="A52" s="9"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="15"/>
-      <c r="B53" s="16"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
+      <c r="A53" s="11"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
     </row>
     <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="11"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
+      <c r="A54" s="9"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="15"/>
-      <c r="B55" s="16"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
+      <c r="A55" s="11"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
     </row>
     <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
+      <c r="A56" s="9"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
     </row>
     <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="15"/>
-      <c r="B57" s="16"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
+      <c r="A57" s="11"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
     </row>
     <row r="58" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="11"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
+      <c r="A58" s="9"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
     </row>
     <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="15"/>
-      <c r="B59" s="16"/>
-      <c r="C59" s="17"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
+      <c r="A59" s="11"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
     </row>
     <row r="60" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
+      <c r="A60" s="9"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
     </row>
     <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="15"/>
-      <c r="B61" s="16"/>
-      <c r="C61" s="17"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
+      <c r="A61" s="11"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
     </row>
     <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="11"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
+      <c r="A62" s="9"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
     </row>
     <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="15"/>
-      <c r="B63" s="16"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
+      <c r="A63" s="11"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
     </row>
     <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="11"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
+      <c r="A64" s="9"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
     </row>
     <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="15"/>
-      <c r="B65" s="16"/>
-      <c r="C65" s="17"/>
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
+      <c r="A65" s="11"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
     </row>
     <row r="66" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="11"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
+      <c r="A66" s="9"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
     </row>
     <row r="67" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="15"/>
-      <c r="B67" s="16"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="18"/>
-      <c r="E67" s="18"/>
+      <c r="A67" s="11"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
     </row>
     <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="11"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
+      <c r="A68" s="9"/>
+      <c r="B68" s="10"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="15"/>
-      <c r="B69" s="16"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="18"/>
-      <c r="E69" s="18"/>
+      <c r="A69" s="11"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
     </row>
     <row r="70" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="11"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
+      <c r="A70" s="9"/>
+      <c r="B70" s="10"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
     </row>
     <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="15"/>
-      <c r="B71" s="16"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="18"/>
+      <c r="A71" s="11"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
     </row>
     <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="11"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
+      <c r="A72" s="9"/>
+      <c r="B72" s="10"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
     </row>
     <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="15"/>
-      <c r="B73" s="16"/>
-      <c r="C73" s="17"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
+      <c r="A73" s="11"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
     </row>
     <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="11"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
+      <c r="A74" s="9"/>
+      <c r="B74" s="10"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="9"/>
     </row>
     <row r="75" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="15"/>
-      <c r="B75" s="16"/>
-      <c r="C75" s="17"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
+      <c r="A75" s="11"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
     </row>
     <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="11"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
+      <c r="A76" s="9"/>
+      <c r="B76" s="10"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="9"/>
     </row>
     <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="15"/>
-      <c r="B77" s="16"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
+      <c r="A77" s="11"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
     </row>
     <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="11"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
+      <c r="A78" s="9"/>
+      <c r="B78" s="10"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
     </row>
     <row r="79" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="15"/>
-      <c r="B79" s="16"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
+      <c r="A79" s="11"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
     </row>
     <row r="80" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="11"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
+      <c r="A80" s="9"/>
+      <c r="B80" s="10"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
     </row>
     <row r="81" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="15"/>
-      <c r="B81" s="16"/>
-      <c r="C81" s="17"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
+      <c r="A81" s="11"/>
+      <c r="B81" s="12"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
     </row>
     <row r="82" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="11"/>
-      <c r="B82" s="12"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
+      <c r="A82" s="9"/>
+      <c r="B82" s="10"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9"/>
     </row>
     <row r="83" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="15"/>
-      <c r="B83" s="16"/>
-      <c r="C83" s="17"/>
-      <c r="D83" s="18"/>
-      <c r="E83" s="18"/>
+      <c r="A83" s="11"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
     </row>
     <row r="84" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="11"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
+      <c r="A84" s="9"/>
+      <c r="B84" s="10"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9"/>
     </row>
     <row r="85" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="15"/>
-      <c r="B85" s="16"/>
-      <c r="C85" s="17"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
+      <c r="A85" s="11"/>
+      <c r="B85" s="12"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
     </row>
     <row r="86" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="11"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="13"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
+      <c r="A86" s="9"/>
+      <c r="B86" s="10"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="9"/>
     </row>
     <row r="87" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="15"/>
-      <c r="B87" s="16"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
+      <c r="A87" s="11"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
     </row>
     <row r="88" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="11"/>
-      <c r="B88" s="12"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
+      <c r="A88" s="9"/>
+      <c r="B88" s="10"/>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="9"/>
     </row>
     <row r="89" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="15"/>
-      <c r="B89" s="16"/>
-      <c r="C89" s="17"/>
-      <c r="D89" s="18"/>
-      <c r="E89" s="18"/>
+      <c r="A89" s="11"/>
+      <c r="B89" s="12"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
     </row>
     <row r="90" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="11"/>
-      <c r="B90" s="12"/>
-      <c r="C90" s="13"/>
-      <c r="D90" s="14"/>
-      <c r="E90" s="14"/>
+      <c r="A90" s="9"/>
+      <c r="B90" s="10"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
     </row>
     <row r="91" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="15"/>
-      <c r="B91" s="16"/>
-      <c r="C91" s="17"/>
-      <c r="D91" s="18"/>
-      <c r="E91" s="18"/>
+      <c r="A91" s="11"/>
+      <c r="B91" s="12"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
     </row>
     <row r="92" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="11"/>
-      <c r="B92" s="12"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="14"/>
-      <c r="E92" s="14"/>
+      <c r="A92" s="9"/>
+      <c r="B92" s="10"/>
+      <c r="C92" s="9"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="9"/>
     </row>
     <row r="93" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="15"/>
-      <c r="B93" s="16"/>
-      <c r="C93" s="17"/>
-      <c r="D93" s="18"/>
-      <c r="E93" s="18"/>
+      <c r="A93" s="11"/>
+      <c r="B93" s="12"/>
+      <c r="C93" s="11"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
     </row>
     <row r="94" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="11"/>
-      <c r="B94" s="12"/>
-      <c r="C94" s="13"/>
-      <c r="D94" s="14"/>
-      <c r="E94" s="14"/>
+      <c r="A94" s="9"/>
+      <c r="B94" s="10"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="9"/>
     </row>
     <row r="95" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="15"/>
-      <c r="B95" s="16"/>
-      <c r="C95" s="17"/>
-      <c r="D95" s="18"/>
-      <c r="E95" s="18"/>
+      <c r="A95" s="11"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
     </row>
     <row r="96" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="11"/>
-      <c r="B96" s="12"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="14"/>
-      <c r="E96" s="14"/>
+      <c r="A96" s="9"/>
+      <c r="B96" s="10"/>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="9"/>
     </row>
     <row r="97" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="15"/>
-      <c r="B97" s="16"/>
-      <c r="C97" s="17"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="18"/>
+      <c r="A97" s="11"/>
+      <c r="B97" s="12"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
     </row>
     <row r="98" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="11"/>
-      <c r="B98" s="12"/>
-      <c r="C98" s="13"/>
-      <c r="D98" s="14"/>
-      <c r="E98" s="14"/>
+      <c r="A98" s="9"/>
+      <c r="B98" s="10"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="9"/>
     </row>
     <row r="99" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="15"/>
-      <c r="B99" s="16"/>
-      <c r="C99" s="17"/>
-      <c r="D99" s="18"/>
-      <c r="E99" s="18"/>
+      <c r="A99" s="11"/>
+      <c r="B99" s="12"/>
+      <c r="C99" s="11"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
     </row>
     <row r="100" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="11"/>
-      <c r="B100" s="12"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="14"/>
-      <c r="E100" s="14"/>
+      <c r="A100" s="9"/>
+      <c r="B100" s="10"/>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9"/>
+      <c r="E100" s="9"/>
     </row>
     <row r="101" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="15"/>
-      <c r="B101" s="16"/>
-      <c r="C101" s="17"/>
-      <c r="D101" s="18"/>
-      <c r="E101" s="18"/>
+      <c r="A101" s="11"/>
+      <c r="B101" s="12"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
     </row>
     <row r="102" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="11"/>
-      <c r="B102" s="12"/>
-      <c r="C102" s="13"/>
-      <c r="D102" s="14"/>
-      <c r="E102" s="14"/>
+      <c r="A102" s="9"/>
+      <c r="B102" s="10"/>
+      <c r="C102" s="9"/>
+      <c r="D102" s="9"/>
+      <c r="E102" s="9"/>
     </row>
     <row r="103" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="15"/>
-      <c r="B103" s="16"/>
-      <c r="C103" s="17"/>
-      <c r="D103" s="18"/>
-      <c r="E103" s="18"/>
+      <c r="A103" s="11"/>
+      <c r="B103" s="12"/>
+      <c r="C103" s="11"/>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
     </row>
     <row r="104" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="11"/>
-      <c r="B104" s="12"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="14"/>
-      <c r="E104" s="14"/>
+      <c r="A104" s="9"/>
+      <c r="B104" s="10"/>
+      <c r="C104" s="9"/>
+      <c r="D104" s="9"/>
+      <c r="E104" s="9"/>
     </row>
     <row r="105" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="15"/>
-      <c r="B105" s="16"/>
-      <c r="C105" s="17"/>
-      <c r="D105" s="18"/>
-      <c r="E105" s="18"/>
+      <c r="A105" s="11"/>
+      <c r="B105" s="12"/>
+      <c r="C105" s="11"/>
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
     </row>
     <row r="106" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="11"/>
-      <c r="B106" s="12"/>
-      <c r="C106" s="13"/>
-      <c r="D106" s="14"/>
-      <c r="E106" s="14"/>
+      <c r="A106" s="9"/>
+      <c r="B106" s="10"/>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9"/>
+      <c r="E106" s="9"/>
     </row>
     <row r="107" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="15"/>
-      <c r="B107" s="16"/>
-      <c r="C107" s="17"/>
-      <c r="D107" s="18"/>
-      <c r="E107" s="18"/>
+      <c r="A107" s="11"/>
+      <c r="B107" s="12"/>
+      <c r="C107" s="11"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
     </row>
     <row r="108" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="11"/>
-      <c r="B108" s="12"/>
-      <c r="C108" s="13"/>
-      <c r="D108" s="14"/>
-      <c r="E108" s="14"/>
+      <c r="A108" s="9"/>
+      <c r="B108" s="10"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9"/>
+      <c r="E108" s="9"/>
     </row>
     <row r="109" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="15"/>
-      <c r="B109" s="16"/>
-      <c r="C109" s="17"/>
-      <c r="D109" s="18"/>
-      <c r="E109" s="18"/>
+      <c r="A109" s="11"/>
+      <c r="B109" s="12"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1628,138 +1575,112 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="80"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>28</v>
+      <c r="A1" s="13" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20"/>
+      <c r="A2" s="14"/>
     </row>
     <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>29</v>
+      <c r="A3" s="15" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>30</v>
+      <c r="A4" s="16" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>31</v>
+      <c r="A5" s="16" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
-        <v>32</v>
+      <c r="A6" s="16" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20"/>
-    </row>
-    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
-        <v>34</v>
+      <c r="A7" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14"/>
+    </row>
+    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="s">
-        <v>35</v>
+      <c r="A10" s="16" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="s">
-        <v>36</v>
+      <c r="A11" s="16" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20"/>
-    </row>
-    <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
-        <v>38</v>
+      <c r="A12" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14"/>
+    </row>
+    <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
-        <v>39</v>
+      <c r="A15" s="16" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20"/>
-    </row>
-    <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
-        <v>40</v>
+      <c r="A16" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22" t="s">
-        <v>41</v>
+      <c r="A18" s="16" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22" t="s">
-        <v>42</v>
+      <c r="A19" s="16" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20"/>
+      <c r="A20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="s">
+      <c r="A21" s="17" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="s">
+    <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20"/>
-    </row>
-    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="25" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
